--- a/histograms/histogram_Temperature__K.xlsx
+++ b/histograms/histogram_Temperature__K.xlsx
@@ -445,7 +445,7 @@
         <v>289.125</v>
       </c>
       <c r="B2" t="n">
-        <v>13420</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>293.625</v>
       </c>
       <c r="B4" t="n">
-        <v>1186</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         <v>298.125</v>
       </c>
       <c r="B6" t="n">
-        <v>10497</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7">
@@ -493,7 +493,7 @@
         <v>302.625</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -597,7 +597,7 @@
         <v>331.875</v>
       </c>
       <c r="B21" t="n">
-        <v>1280</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
